--- a/nr-update-idnatstruct-descr/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/nr-update-idnatstruct-descr/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T15:39:50+00:00</t>
+    <t>2025-02-04T15:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
